--- a/기획문서/LALA 테이블 명세서.xlsx
+++ b/기획문서/LALA 테이블 명세서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\siwoo\Desktop\최종프로젝트\기획문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEB47E8-875C-4777-86E6-F8EBC061E040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4658A4-4C77-4AD6-AE8B-39DC9A43B586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{05088ACD-AF11-4393-B831-36F7C64AFD8E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1362" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1361" uniqueCount="379">
   <si>
     <t>user</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2217,12 +2217,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2245,6 +2239,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2640,35 +2640,35 @@
       <c r="B2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="49"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="47"/>
     </row>
     <row r="3" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="48" t="s">
         <v>238</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="52"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="50"/>
     </row>
     <row r="4" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="10" t="s">
@@ -2845,35 +2845,35 @@
       <c r="B11" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="45" t="s">
         <v>350</v>
       </c>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="48"/>
-      <c r="J11" s="48"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="49"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="47"/>
     </row>
     <row r="12" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="52"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="49"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="50"/>
     </row>
     <row r="13" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="10" t="s">
@@ -2957,18 +2957,18 @@
       <c r="B17" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C17" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="46"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="53"/>
+      <c r="J17" s="53"/>
+      <c r="K17" s="53"/>
+      <c r="L17" s="54"/>
     </row>
     <row r="18" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="10" t="s">
@@ -3072,35 +3072,35 @@
       <c r="B22" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="53" t="s">
+      <c r="C22" s="51" t="s">
         <v>344</v>
       </c>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="54"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+      <c r="L22" s="52"/>
     </row>
     <row r="23" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="53" t="s">
         <v>345</v>
       </c>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="45"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="45"/>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="46"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="54"/>
     </row>
     <row r="24" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="10" t="s">
@@ -3234,18 +3234,18 @@
       <c r="B30" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="50" t="s">
+      <c r="C30" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="52"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
+      <c r="L30" s="50"/>
     </row>
     <row r="31" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="10" t="s">
@@ -3553,18 +3553,18 @@
       <c r="B43" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="51"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="51"/>
-      <c r="K43" s="51"/>
-      <c r="L43" s="52"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
+      <c r="J43" s="49"/>
+      <c r="K43" s="49"/>
+      <c r="L43" s="50"/>
     </row>
     <row r="44" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B44" s="10" t="s">
@@ -3706,18 +3706,18 @@
       <c r="B50" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="50" t="s">
+      <c r="C50" s="48" t="s">
         <v>357</v>
       </c>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="52"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="49"/>
+      <c r="I50" s="49"/>
+      <c r="J50" s="49"/>
+      <c r="K50" s="49"/>
+      <c r="L50" s="50"/>
     </row>
     <row r="51" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B51" s="10" t="s">
@@ -3808,18 +3808,18 @@
       <c r="B55" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="51"/>
-      <c r="K55" s="51"/>
-      <c r="L55" s="52"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="50"/>
     </row>
     <row r="56" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B56" s="10" t="s">
@@ -3974,18 +3974,18 @@
       <c r="B63" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="51"/>
-      <c r="L63" s="52"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="49"/>
+      <c r="L63" s="50"/>
     </row>
     <row r="64" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B64" s="10" t="s">
@@ -4100,18 +4100,18 @@
       <c r="B69" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="50" t="s">
+      <c r="C69" s="48" t="s">
         <v>358</v>
       </c>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="51"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
-      <c r="J69" s="51"/>
-      <c r="K69" s="51"/>
-      <c r="L69" s="52"/>
+      <c r="D69" s="49"/>
+      <c r="E69" s="49"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="49"/>
+      <c r="L69" s="50"/>
     </row>
     <row r="70" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B70" s="10" t="s">
@@ -4195,18 +4195,18 @@
       <c r="B74" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C74" s="50" t="s">
+      <c r="C74" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="51"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="51"/>
-      <c r="I74" s="51"/>
-      <c r="J74" s="51"/>
-      <c r="K74" s="51"/>
-      <c r="L74" s="52"/>
+      <c r="D74" s="49"/>
+      <c r="E74" s="49"/>
+      <c r="F74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="49"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="49"/>
+      <c r="L74" s="50"/>
     </row>
     <row r="75" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B75" s="10" t="s">
@@ -4578,35 +4578,35 @@
       <c r="B90" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="53" t="s">
+      <c r="C90" s="51" t="s">
         <v>203</v>
       </c>
-      <c r="D90" s="53"/>
-      <c r="E90" s="53"/>
-      <c r="F90" s="53"/>
-      <c r="G90" s="53"/>
-      <c r="H90" s="53"/>
-      <c r="I90" s="53"/>
-      <c r="J90" s="53"/>
-      <c r="K90" s="53"/>
-      <c r="L90" s="54"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="51"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="51"/>
+      <c r="H90" s="51"/>
+      <c r="I90" s="51"/>
+      <c r="J90" s="51"/>
+      <c r="K90" s="51"/>
+      <c r="L90" s="52"/>
     </row>
     <row r="91" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B91" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C91" s="45" t="s">
+      <c r="C91" s="53" t="s">
         <v>204</v>
       </c>
-      <c r="D91" s="45"/>
-      <c r="E91" s="45"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="45"/>
-      <c r="K91" s="45"/>
-      <c r="L91" s="46"/>
+      <c r="D91" s="53"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="53"/>
+      <c r="I91" s="53"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="54"/>
     </row>
     <row r="92" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B92" s="10" t="s">
@@ -4782,18 +4782,18 @@
       <c r="B99" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C99" s="50" t="s">
+      <c r="C99" s="48" t="s">
         <v>359</v>
       </c>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="51"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
-      <c r="J99" s="51"/>
-      <c r="K99" s="51"/>
-      <c r="L99" s="52"/>
+      <c r="D99" s="49"/>
+      <c r="E99" s="49"/>
+      <c r="F99" s="49"/>
+      <c r="G99" s="49"/>
+      <c r="H99" s="49"/>
+      <c r="I99" s="49"/>
+      <c r="J99" s="49"/>
+      <c r="K99" s="49"/>
+      <c r="L99" s="50"/>
     </row>
     <row r="100" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B100" s="10" t="s">
@@ -4867,35 +4867,35 @@
       <c r="B103" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C103" s="53" t="s">
+      <c r="C103" s="51" t="s">
         <v>211</v>
       </c>
-      <c r="D103" s="53"/>
-      <c r="E103" s="53"/>
-      <c r="F103" s="53"/>
-      <c r="G103" s="53"/>
-      <c r="H103" s="53"/>
-      <c r="I103" s="53"/>
-      <c r="J103" s="53"/>
-      <c r="K103" s="53"/>
-      <c r="L103" s="54"/>
+      <c r="D103" s="51"/>
+      <c r="E103" s="51"/>
+      <c r="F103" s="51"/>
+      <c r="G103" s="51"/>
+      <c r="H103" s="51"/>
+      <c r="I103" s="51"/>
+      <c r="J103" s="51"/>
+      <c r="K103" s="51"/>
+      <c r="L103" s="52"/>
     </row>
     <row r="104" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B104" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C104" s="45" t="s">
+      <c r="C104" s="53" t="s">
         <v>212</v>
       </c>
-      <c r="D104" s="45"/>
-      <c r="E104" s="45"/>
-      <c r="F104" s="45"/>
-      <c r="G104" s="45"/>
-      <c r="H104" s="45"/>
-      <c r="I104" s="45"/>
-      <c r="J104" s="45"/>
-      <c r="K104" s="45"/>
-      <c r="L104" s="46"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
+      <c r="I104" s="53"/>
+      <c r="J104" s="53"/>
+      <c r="K104" s="53"/>
+      <c r="L104" s="54"/>
     </row>
     <row r="105" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B105" s="10" t="s">
@@ -5103,35 +5103,35 @@
       <c r="B113" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C113" s="53" t="s">
+      <c r="C113" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="D113" s="53"/>
-      <c r="E113" s="53"/>
-      <c r="F113" s="53"/>
-      <c r="G113" s="53"/>
-      <c r="H113" s="53"/>
-      <c r="I113" s="53"/>
-      <c r="J113" s="53"/>
-      <c r="K113" s="53"/>
-      <c r="L113" s="54"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="51"/>
+      <c r="F113" s="51"/>
+      <c r="G113" s="51"/>
+      <c r="H113" s="51"/>
+      <c r="I113" s="51"/>
+      <c r="J113" s="51"/>
+      <c r="K113" s="51"/>
+      <c r="L113" s="52"/>
     </row>
     <row r="114" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B114" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C114" s="45" t="s">
+      <c r="C114" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="D114" s="45"/>
-      <c r="E114" s="45"/>
-      <c r="F114" s="45"/>
-      <c r="G114" s="45"/>
-      <c r="H114" s="45"/>
-      <c r="I114" s="45"/>
-      <c r="J114" s="45"/>
-      <c r="K114" s="45"/>
-      <c r="L114" s="46"/>
+      <c r="D114" s="53"/>
+      <c r="E114" s="53"/>
+      <c r="F114" s="53"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="53"/>
+      <c r="I114" s="53"/>
+      <c r="J114" s="53"/>
+      <c r="K114" s="53"/>
+      <c r="L114" s="54"/>
     </row>
     <row r="115" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B115" s="10" t="s">
@@ -5256,35 +5256,35 @@
       <c r="B120" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C120" s="53" t="s">
+      <c r="C120" s="51" t="s">
         <v>271</v>
       </c>
-      <c r="D120" s="53"/>
-      <c r="E120" s="53"/>
-      <c r="F120" s="53"/>
-      <c r="G120" s="53"/>
-      <c r="H120" s="53"/>
-      <c r="I120" s="53"/>
-      <c r="J120" s="53"/>
-      <c r="K120" s="53"/>
-      <c r="L120" s="54"/>
+      <c r="D120" s="51"/>
+      <c r="E120" s="51"/>
+      <c r="F120" s="51"/>
+      <c r="G120" s="51"/>
+      <c r="H120" s="51"/>
+      <c r="I120" s="51"/>
+      <c r="J120" s="51"/>
+      <c r="K120" s="51"/>
+      <c r="L120" s="52"/>
     </row>
     <row r="121" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B121" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C121" s="45" t="s">
+      <c r="C121" s="53" t="s">
         <v>272</v>
       </c>
-      <c r="D121" s="45"/>
-      <c r="E121" s="45"/>
-      <c r="F121" s="45"/>
-      <c r="G121" s="45"/>
-      <c r="H121" s="45"/>
-      <c r="I121" s="45"/>
-      <c r="J121" s="45"/>
-      <c r="K121" s="45"/>
-      <c r="L121" s="46"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="53"/>
+      <c r="F121" s="53"/>
+      <c r="G121" s="53"/>
+      <c r="H121" s="53"/>
+      <c r="I121" s="53"/>
+      <c r="J121" s="53"/>
+      <c r="K121" s="53"/>
+      <c r="L121" s="54"/>
     </row>
     <row r="122" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B122" s="10" t="s">
@@ -5496,35 +5496,35 @@
       <c r="B130" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C130" s="53" t="s">
+      <c r="C130" s="51" t="s">
         <v>354</v>
       </c>
-      <c r="D130" s="53"/>
-      <c r="E130" s="53"/>
-      <c r="F130" s="53"/>
-      <c r="G130" s="53"/>
-      <c r="H130" s="53"/>
-      <c r="I130" s="53"/>
-      <c r="J130" s="53"/>
-      <c r="K130" s="53"/>
-      <c r="L130" s="54"/>
+      <c r="D130" s="51"/>
+      <c r="E130" s="51"/>
+      <c r="F130" s="51"/>
+      <c r="G130" s="51"/>
+      <c r="H130" s="51"/>
+      <c r="I130" s="51"/>
+      <c r="J130" s="51"/>
+      <c r="K130" s="51"/>
+      <c r="L130" s="52"/>
     </row>
     <row r="131" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B131" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C131" s="45" t="s">
+      <c r="C131" s="53" t="s">
         <v>355</v>
       </c>
-      <c r="D131" s="45"/>
-      <c r="E131" s="45"/>
-      <c r="F131" s="45"/>
-      <c r="G131" s="45"/>
-      <c r="H131" s="45"/>
-      <c r="I131" s="45"/>
-      <c r="J131" s="45"/>
-      <c r="K131" s="45"/>
-      <c r="L131" s="46"/>
+      <c r="D131" s="53"/>
+      <c r="E131" s="53"/>
+      <c r="F131" s="53"/>
+      <c r="G131" s="53"/>
+      <c r="H131" s="53"/>
+      <c r="I131" s="53"/>
+      <c r="J131" s="53"/>
+      <c r="K131" s="53"/>
+      <c r="L131" s="54"/>
     </row>
     <row r="132" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B132" s="10" t="s">
@@ -5591,35 +5591,35 @@
       <c r="B135" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="53" t="s">
+      <c r="C135" s="51" t="s">
         <v>330</v>
       </c>
-      <c r="D135" s="53"/>
-      <c r="E135" s="53"/>
-      <c r="F135" s="53"/>
-      <c r="G135" s="53"/>
-      <c r="H135" s="53"/>
-      <c r="I135" s="53"/>
-      <c r="J135" s="53"/>
-      <c r="K135" s="53"/>
-      <c r="L135" s="54"/>
+      <c r="D135" s="51"/>
+      <c r="E135" s="51"/>
+      <c r="F135" s="51"/>
+      <c r="G135" s="51"/>
+      <c r="H135" s="51"/>
+      <c r="I135" s="51"/>
+      <c r="J135" s="51"/>
+      <c r="K135" s="51"/>
+      <c r="L135" s="52"/>
     </row>
     <row r="136" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B136" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C136" s="45" t="s">
+      <c r="C136" s="53" t="s">
         <v>331</v>
       </c>
-      <c r="D136" s="45"/>
-      <c r="E136" s="45"/>
-      <c r="F136" s="45"/>
-      <c r="G136" s="45"/>
-      <c r="H136" s="45"/>
-      <c r="I136" s="45"/>
-      <c r="J136" s="45"/>
-      <c r="K136" s="45"/>
-      <c r="L136" s="46"/>
+      <c r="D136" s="53"/>
+      <c r="E136" s="53"/>
+      <c r="F136" s="53"/>
+      <c r="G136" s="53"/>
+      <c r="H136" s="53"/>
+      <c r="I136" s="53"/>
+      <c r="J136" s="53"/>
+      <c r="K136" s="53"/>
+      <c r="L136" s="54"/>
     </row>
     <row r="137" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B137" s="10" t="s">
@@ -5813,18 +5813,18 @@
       <c r="B145" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C145" s="50" t="s">
+      <c r="C145" s="48" t="s">
         <v>93</v>
       </c>
-      <c r="D145" s="51"/>
-      <c r="E145" s="51"/>
-      <c r="F145" s="51"/>
-      <c r="G145" s="51"/>
-      <c r="H145" s="51"/>
-      <c r="I145" s="51"/>
-      <c r="J145" s="51"/>
-      <c r="K145" s="51"/>
-      <c r="L145" s="52"/>
+      <c r="D145" s="49"/>
+      <c r="E145" s="49"/>
+      <c r="F145" s="49"/>
+      <c r="G145" s="49"/>
+      <c r="H145" s="49"/>
+      <c r="I145" s="49"/>
+      <c r="J145" s="49"/>
+      <c r="K145" s="49"/>
+      <c r="L145" s="50"/>
     </row>
     <row r="146" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B146" s="10" t="s">
@@ -5942,18 +5942,18 @@
       <c r="B151" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C151" s="50" t="s">
+      <c r="C151" s="48" t="s">
         <v>326</v>
       </c>
-      <c r="D151" s="51"/>
-      <c r="E151" s="51"/>
-      <c r="F151" s="51"/>
-      <c r="G151" s="51"/>
-      <c r="H151" s="51"/>
-      <c r="I151" s="51"/>
-      <c r="J151" s="51"/>
-      <c r="K151" s="51"/>
-      <c r="L151" s="52"/>
+      <c r="D151" s="49"/>
+      <c r="E151" s="49"/>
+      <c r="F151" s="49"/>
+      <c r="G151" s="49"/>
+      <c r="H151" s="49"/>
+      <c r="I151" s="49"/>
+      <c r="J151" s="49"/>
+      <c r="K151" s="49"/>
+      <c r="L151" s="50"/>
     </row>
     <row r="152" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B152" s="10" t="s">
@@ -6099,35 +6099,35 @@
       <c r="B158" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C158" s="53" t="s">
+      <c r="C158" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="D158" s="53"/>
-      <c r="E158" s="53"/>
-      <c r="F158" s="53"/>
-      <c r="G158" s="53"/>
-      <c r="H158" s="53"/>
-      <c r="I158" s="53"/>
-      <c r="J158" s="53"/>
-      <c r="K158" s="53"/>
-      <c r="L158" s="54"/>
+      <c r="D158" s="51"/>
+      <c r="E158" s="51"/>
+      <c r="F158" s="51"/>
+      <c r="G158" s="51"/>
+      <c r="H158" s="51"/>
+      <c r="I158" s="51"/>
+      <c r="J158" s="51"/>
+      <c r="K158" s="51"/>
+      <c r="L158" s="52"/>
     </row>
     <row r="159" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B159" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C159" s="45" t="s">
+      <c r="C159" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="D159" s="45"/>
-      <c r="E159" s="45"/>
-      <c r="F159" s="45"/>
-      <c r="G159" s="45"/>
-      <c r="H159" s="45"/>
-      <c r="I159" s="45"/>
-      <c r="J159" s="45"/>
-      <c r="K159" s="45"/>
-      <c r="L159" s="46"/>
+      <c r="D159" s="53"/>
+      <c r="E159" s="53"/>
+      <c r="F159" s="53"/>
+      <c r="G159" s="53"/>
+      <c r="H159" s="53"/>
+      <c r="I159" s="53"/>
+      <c r="J159" s="53"/>
+      <c r="K159" s="53"/>
+      <c r="L159" s="54"/>
     </row>
     <row r="160" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B160" s="10" t="s">
@@ -6232,35 +6232,35 @@
       <c r="B164" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C164" s="53" t="s">
+      <c r="C164" s="51" t="s">
         <v>360</v>
       </c>
-      <c r="D164" s="53"/>
-      <c r="E164" s="53"/>
-      <c r="F164" s="53"/>
-      <c r="G164" s="53"/>
-      <c r="H164" s="53"/>
-      <c r="I164" s="53"/>
-      <c r="J164" s="53"/>
-      <c r="K164" s="53"/>
-      <c r="L164" s="54"/>
+      <c r="D164" s="51"/>
+      <c r="E164" s="51"/>
+      <c r="F164" s="51"/>
+      <c r="G164" s="51"/>
+      <c r="H164" s="51"/>
+      <c r="I164" s="51"/>
+      <c r="J164" s="51"/>
+      <c r="K164" s="51"/>
+      <c r="L164" s="52"/>
     </row>
     <row r="165" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B165" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C165" s="45" t="s">
+      <c r="C165" s="53" t="s">
         <v>362</v>
       </c>
-      <c r="D165" s="45"/>
-      <c r="E165" s="45"/>
-      <c r="F165" s="45"/>
-      <c r="G165" s="45"/>
-      <c r="H165" s="45"/>
-      <c r="I165" s="45"/>
-      <c r="J165" s="45"/>
-      <c r="K165" s="45"/>
-      <c r="L165" s="46"/>
+      <c r="D165" s="53"/>
+      <c r="E165" s="53"/>
+      <c r="F165" s="53"/>
+      <c r="G165" s="53"/>
+      <c r="H165" s="53"/>
+      <c r="I165" s="53"/>
+      <c r="J165" s="53"/>
+      <c r="K165" s="53"/>
+      <c r="L165" s="54"/>
     </row>
     <row r="166" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B166" s="10" t="s">
@@ -6344,18 +6344,18 @@
       <c r="B170" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C170" s="50" t="s">
+      <c r="C170" s="48" t="s">
         <v>258</v>
       </c>
-      <c r="D170" s="51"/>
-      <c r="E170" s="51"/>
-      <c r="F170" s="51"/>
-      <c r="G170" s="51"/>
-      <c r="H170" s="51"/>
-      <c r="I170" s="51"/>
-      <c r="J170" s="51"/>
-      <c r="K170" s="51"/>
-      <c r="L170" s="52"/>
+      <c r="D170" s="49"/>
+      <c r="E170" s="49"/>
+      <c r="F170" s="49"/>
+      <c r="G170" s="49"/>
+      <c r="H170" s="49"/>
+      <c r="I170" s="49"/>
+      <c r="J170" s="49"/>
+      <c r="K170" s="49"/>
+      <c r="L170" s="50"/>
     </row>
     <row r="171" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B171" s="10" t="s">
@@ -6472,18 +6472,18 @@
       <c r="B176" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C176" s="50" t="s">
+      <c r="C176" s="48" t="s">
         <v>316</v>
       </c>
-      <c r="D176" s="51"/>
-      <c r="E176" s="51"/>
-      <c r="F176" s="51"/>
-      <c r="G176" s="51"/>
-      <c r="H176" s="51"/>
-      <c r="I176" s="51"/>
-      <c r="J176" s="51"/>
-      <c r="K176" s="51"/>
-      <c r="L176" s="52"/>
+      <c r="D176" s="49"/>
+      <c r="E176" s="49"/>
+      <c r="F176" s="49"/>
+      <c r="G176" s="49"/>
+      <c r="H176" s="49"/>
+      <c r="I176" s="49"/>
+      <c r="J176" s="49"/>
+      <c r="K176" s="49"/>
+      <c r="L176" s="50"/>
     </row>
     <row r="177" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B177" s="10" t="s">
@@ -6557,35 +6557,35 @@
       <c r="B180" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C180" s="47" t="s">
+      <c r="C180" s="45" t="s">
         <v>265</v>
       </c>
-      <c r="D180" s="48"/>
-      <c r="E180" s="48"/>
-      <c r="F180" s="48"/>
-      <c r="G180" s="48"/>
-      <c r="H180" s="48"/>
-      <c r="I180" s="48"/>
-      <c r="J180" s="48"/>
-      <c r="K180" s="48"/>
-      <c r="L180" s="49"/>
+      <c r="D180" s="46"/>
+      <c r="E180" s="46"/>
+      <c r="F180" s="46"/>
+      <c r="G180" s="46"/>
+      <c r="H180" s="46"/>
+      <c r="I180" s="46"/>
+      <c r="J180" s="46"/>
+      <c r="K180" s="46"/>
+      <c r="L180" s="47"/>
     </row>
     <row r="181" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B181" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C181" s="50" t="s">
+      <c r="C181" s="48" t="s">
         <v>266</v>
       </c>
-      <c r="D181" s="51"/>
-      <c r="E181" s="51"/>
-      <c r="F181" s="51"/>
-      <c r="G181" s="51"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="51"/>
-      <c r="J181" s="51"/>
-      <c r="K181" s="51"/>
-      <c r="L181" s="52"/>
+      <c r="D181" s="49"/>
+      <c r="E181" s="49"/>
+      <c r="F181" s="49"/>
+      <c r="G181" s="49"/>
+      <c r="H181" s="49"/>
+      <c r="I181" s="49"/>
+      <c r="J181" s="49"/>
+      <c r="K181" s="49"/>
+      <c r="L181" s="50"/>
     </row>
     <row r="182" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B182" s="10" t="s">
@@ -6740,35 +6740,35 @@
       <c r="B188" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C188" s="45" t="s">
+      <c r="C188" s="53" t="s">
         <v>346</v>
       </c>
-      <c r="D188" s="45"/>
-      <c r="E188" s="45"/>
-      <c r="F188" s="45"/>
-      <c r="G188" s="45"/>
-      <c r="H188" s="45"/>
-      <c r="I188" s="45"/>
-      <c r="J188" s="45"/>
-      <c r="K188" s="45"/>
-      <c r="L188" s="45"/>
+      <c r="D188" s="53"/>
+      <c r="E188" s="53"/>
+      <c r="F188" s="53"/>
+      <c r="G188" s="53"/>
+      <c r="H188" s="53"/>
+      <c r="I188" s="53"/>
+      <c r="J188" s="53"/>
+      <c r="K188" s="53"/>
+      <c r="L188" s="53"/>
     </row>
     <row r="189" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B189" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C189" s="45" t="s">
+      <c r="C189" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="D189" s="45"/>
-      <c r="E189" s="45"/>
-      <c r="F189" s="45"/>
-      <c r="G189" s="45"/>
-      <c r="H189" s="45"/>
-      <c r="I189" s="45"/>
-      <c r="J189" s="45"/>
-      <c r="K189" s="45"/>
-      <c r="L189" s="45"/>
+      <c r="D189" s="53"/>
+      <c r="E189" s="53"/>
+      <c r="F189" s="53"/>
+      <c r="G189" s="53"/>
+      <c r="H189" s="53"/>
+      <c r="I189" s="53"/>
+      <c r="J189" s="53"/>
+      <c r="K189" s="53"/>
+      <c r="L189" s="53"/>
     </row>
     <row r="190" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B190" s="11" t="s">
@@ -6926,18 +6926,18 @@
       <c r="B197" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C197" s="50" t="s">
+      <c r="C197" s="48" t="s">
         <v>107</v>
       </c>
-      <c r="D197" s="51"/>
-      <c r="E197" s="51"/>
-      <c r="F197" s="51"/>
-      <c r="G197" s="51"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="51"/>
-      <c r="J197" s="51"/>
-      <c r="K197" s="51"/>
-      <c r="L197" s="52"/>
+      <c r="D197" s="49"/>
+      <c r="E197" s="49"/>
+      <c r="F197" s="49"/>
+      <c r="G197" s="49"/>
+      <c r="H197" s="49"/>
+      <c r="I197" s="49"/>
+      <c r="J197" s="49"/>
+      <c r="K197" s="49"/>
+      <c r="L197" s="50"/>
     </row>
     <row r="198" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B198" s="10" t="s">
@@ -7265,18 +7265,18 @@
       <c r="B211" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C211" s="50" t="s">
+      <c r="C211" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="D211" s="51"/>
-      <c r="E211" s="51"/>
-      <c r="F211" s="51"/>
-      <c r="G211" s="51"/>
-      <c r="H211" s="51"/>
-      <c r="I211" s="51"/>
-      <c r="J211" s="51"/>
-      <c r="K211" s="51"/>
-      <c r="L211" s="52"/>
+      <c r="D211" s="49"/>
+      <c r="E211" s="49"/>
+      <c r="F211" s="49"/>
+      <c r="G211" s="49"/>
+      <c r="H211" s="49"/>
+      <c r="I211" s="49"/>
+      <c r="J211" s="49"/>
+      <c r="K211" s="49"/>
+      <c r="L211" s="50"/>
     </row>
     <row r="212" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B212" s="10" t="s">
@@ -7477,18 +7477,18 @@
       <c r="B220" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C220" s="50" t="s">
+      <c r="C220" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="D220" s="51"/>
-      <c r="E220" s="51"/>
-      <c r="F220" s="51"/>
-      <c r="G220" s="51"/>
-      <c r="H220" s="51"/>
-      <c r="I220" s="51"/>
-      <c r="J220" s="51"/>
-      <c r="K220" s="51"/>
-      <c r="L220" s="52"/>
+      <c r="D220" s="49"/>
+      <c r="E220" s="49"/>
+      <c r="F220" s="49"/>
+      <c r="G220" s="49"/>
+      <c r="H220" s="49"/>
+      <c r="I220" s="49"/>
+      <c r="J220" s="49"/>
+      <c r="K220" s="49"/>
+      <c r="L220" s="50"/>
     </row>
     <row r="221" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B221" s="10" t="s">
@@ -7637,18 +7637,18 @@
       <c r="B227" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C227" s="50" t="s">
+      <c r="C227" s="48" t="s">
         <v>364</v>
       </c>
-      <c r="D227" s="51"/>
-      <c r="E227" s="51"/>
-      <c r="F227" s="51"/>
-      <c r="G227" s="51"/>
-      <c r="H227" s="51"/>
-      <c r="I227" s="51"/>
-      <c r="J227" s="51"/>
-      <c r="K227" s="51"/>
-      <c r="L227" s="52"/>
+      <c r="D227" s="49"/>
+      <c r="E227" s="49"/>
+      <c r="F227" s="49"/>
+      <c r="G227" s="49"/>
+      <c r="H227" s="49"/>
+      <c r="I227" s="49"/>
+      <c r="J227" s="49"/>
+      <c r="K227" s="49"/>
+      <c r="L227" s="50"/>
     </row>
     <row r="228" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B228" s="10" t="s">
@@ -7722,35 +7722,35 @@
       <c r="B231" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C231" s="53" t="s">
+      <c r="C231" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="D231" s="53"/>
-      <c r="E231" s="53"/>
-      <c r="F231" s="53"/>
-      <c r="G231" s="53"/>
-      <c r="H231" s="53"/>
-      <c r="I231" s="53"/>
-      <c r="J231" s="53"/>
-      <c r="K231" s="53"/>
-      <c r="L231" s="54"/>
+      <c r="D231" s="51"/>
+      <c r="E231" s="51"/>
+      <c r="F231" s="51"/>
+      <c r="G231" s="51"/>
+      <c r="H231" s="51"/>
+      <c r="I231" s="51"/>
+      <c r="J231" s="51"/>
+      <c r="K231" s="51"/>
+      <c r="L231" s="52"/>
     </row>
     <row r="232" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B232" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C232" s="45" t="s">
+      <c r="C232" s="53" t="s">
         <v>289</v>
       </c>
-      <c r="D232" s="45"/>
-      <c r="E232" s="45"/>
-      <c r="F232" s="45"/>
-      <c r="G232" s="45"/>
-      <c r="H232" s="45"/>
-      <c r="I232" s="45"/>
-      <c r="J232" s="45"/>
-      <c r="K232" s="45"/>
-      <c r="L232" s="46"/>
+      <c r="D232" s="53"/>
+      <c r="E232" s="53"/>
+      <c r="F232" s="53"/>
+      <c r="G232" s="53"/>
+      <c r="H232" s="53"/>
+      <c r="I232" s="53"/>
+      <c r="J232" s="53"/>
+      <c r="K232" s="53"/>
+      <c r="L232" s="54"/>
     </row>
     <row r="233" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B233" s="10" t="s">
@@ -8113,35 +8113,35 @@
       <c r="B247" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C247" s="53" t="s">
+      <c r="C247" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="D247" s="53"/>
-      <c r="E247" s="53"/>
-      <c r="F247" s="53"/>
-      <c r="G247" s="53"/>
-      <c r="H247" s="53"/>
-      <c r="I247" s="53"/>
-      <c r="J247" s="53"/>
-      <c r="K247" s="53"/>
-      <c r="L247" s="54"/>
+      <c r="D247" s="51"/>
+      <c r="E247" s="51"/>
+      <c r="F247" s="51"/>
+      <c r="G247" s="51"/>
+      <c r="H247" s="51"/>
+      <c r="I247" s="51"/>
+      <c r="J247" s="51"/>
+      <c r="K247" s="51"/>
+      <c r="L247" s="52"/>
     </row>
     <row r="248" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B248" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C248" s="45" t="s">
+      <c r="C248" s="53" t="s">
         <v>248</v>
       </c>
-      <c r="D248" s="45"/>
-      <c r="E248" s="45"/>
-      <c r="F248" s="45"/>
-      <c r="G248" s="45"/>
-      <c r="H248" s="45"/>
-      <c r="I248" s="45"/>
-      <c r="J248" s="45"/>
-      <c r="K248" s="45"/>
-      <c r="L248" s="46"/>
+      <c r="D248" s="53"/>
+      <c r="E248" s="53"/>
+      <c r="F248" s="53"/>
+      <c r="G248" s="53"/>
+      <c r="H248" s="53"/>
+      <c r="I248" s="53"/>
+      <c r="J248" s="53"/>
+      <c r="K248" s="53"/>
+      <c r="L248" s="54"/>
     </row>
     <row r="249" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B249" s="10" t="s">
@@ -8246,9 +8246,7 @@
         <v>500</v>
       </c>
       <c r="F252" s="3"/>
-      <c r="G252" s="3" t="s">
-        <v>19</v>
-      </c>
+      <c r="G252" s="3"/>
       <c r="H252" s="3"/>
       <c r="I252" s="5"/>
       <c r="J252" s="4" t="s">
@@ -8296,35 +8294,35 @@
       <c r="B255" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C255" s="53" t="s">
+      <c r="C255" s="51" t="s">
         <v>365</v>
       </c>
-      <c r="D255" s="53"/>
-      <c r="E255" s="53"/>
-      <c r="F255" s="53"/>
-      <c r="G255" s="53"/>
-      <c r="H255" s="53"/>
-      <c r="I255" s="53"/>
-      <c r="J255" s="53"/>
-      <c r="K255" s="53"/>
-      <c r="L255" s="54"/>
+      <c r="D255" s="51"/>
+      <c r="E255" s="51"/>
+      <c r="F255" s="51"/>
+      <c r="G255" s="51"/>
+      <c r="H255" s="51"/>
+      <c r="I255" s="51"/>
+      <c r="J255" s="51"/>
+      <c r="K255" s="51"/>
+      <c r="L255" s="52"/>
     </row>
     <row r="256" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B256" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C256" s="45" t="s">
+      <c r="C256" s="53" t="s">
         <v>367</v>
       </c>
-      <c r="D256" s="45"/>
-      <c r="E256" s="45"/>
-      <c r="F256" s="45"/>
-      <c r="G256" s="45"/>
-      <c r="H256" s="45"/>
-      <c r="I256" s="45"/>
-      <c r="J256" s="45"/>
-      <c r="K256" s="45"/>
-      <c r="L256" s="46"/>
+      <c r="D256" s="53"/>
+      <c r="E256" s="53"/>
+      <c r="F256" s="53"/>
+      <c r="G256" s="53"/>
+      <c r="H256" s="53"/>
+      <c r="I256" s="53"/>
+      <c r="J256" s="53"/>
+      <c r="K256" s="53"/>
+      <c r="L256" s="54"/>
     </row>
     <row r="257" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B257" s="10" t="s">
@@ -8415,18 +8413,18 @@
       <c r="B261" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C261" s="50" t="s">
+      <c r="C261" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="D261" s="51"/>
-      <c r="E261" s="51"/>
-      <c r="F261" s="51"/>
-      <c r="G261" s="51"/>
-      <c r="H261" s="51"/>
-      <c r="I261" s="51"/>
-      <c r="J261" s="51"/>
-      <c r="K261" s="51"/>
-      <c r="L261" s="52"/>
+      <c r="D261" s="49"/>
+      <c r="E261" s="49"/>
+      <c r="F261" s="49"/>
+      <c r="G261" s="49"/>
+      <c r="H261" s="49"/>
+      <c r="I261" s="49"/>
+      <c r="J261" s="49"/>
+      <c r="K261" s="49"/>
+      <c r="L261" s="50"/>
     </row>
     <row r="262" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B262" s="10" t="s">
@@ -8773,18 +8771,18 @@
       <c r="B276" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C276" s="50" t="s">
+      <c r="C276" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="D276" s="51"/>
-      <c r="E276" s="51"/>
-      <c r="F276" s="51"/>
-      <c r="G276" s="51"/>
-      <c r="H276" s="51"/>
-      <c r="I276" s="51"/>
-      <c r="J276" s="51"/>
-      <c r="K276" s="51"/>
-      <c r="L276" s="52"/>
+      <c r="D276" s="49"/>
+      <c r="E276" s="49"/>
+      <c r="F276" s="49"/>
+      <c r="G276" s="49"/>
+      <c r="H276" s="49"/>
+      <c r="I276" s="49"/>
+      <c r="J276" s="49"/>
+      <c r="K276" s="49"/>
+      <c r="L276" s="50"/>
     </row>
     <row r="277" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B277" s="10" t="s">
@@ -8858,35 +8856,35 @@
       <c r="B280" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C280" s="53" t="s">
+      <c r="C280" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D280" s="53"/>
-      <c r="E280" s="53"/>
-      <c r="F280" s="53"/>
-      <c r="G280" s="53"/>
-      <c r="H280" s="53"/>
-      <c r="I280" s="53"/>
-      <c r="J280" s="53"/>
-      <c r="K280" s="53"/>
-      <c r="L280" s="54"/>
+      <c r="D280" s="51"/>
+      <c r="E280" s="51"/>
+      <c r="F280" s="51"/>
+      <c r="G280" s="51"/>
+      <c r="H280" s="51"/>
+      <c r="I280" s="51"/>
+      <c r="J280" s="51"/>
+      <c r="K280" s="51"/>
+      <c r="L280" s="52"/>
     </row>
     <row r="281" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B281" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C281" s="45" t="s">
+      <c r="C281" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="D281" s="45"/>
-      <c r="E281" s="45"/>
-      <c r="F281" s="45"/>
-      <c r="G281" s="45"/>
-      <c r="H281" s="45"/>
-      <c r="I281" s="45"/>
-      <c r="J281" s="45"/>
-      <c r="K281" s="45"/>
-      <c r="L281" s="46"/>
+      <c r="D281" s="53"/>
+      <c r="E281" s="53"/>
+      <c r="F281" s="53"/>
+      <c r="G281" s="53"/>
+      <c r="H281" s="53"/>
+      <c r="I281" s="53"/>
+      <c r="J281" s="53"/>
+      <c r="K281" s="53"/>
+      <c r="L281" s="54"/>
     </row>
     <row r="282" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B282" s="10" t="s">
@@ -9174,18 +9172,18 @@
       <c r="B294" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C294" s="50" t="s">
+      <c r="C294" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="D294" s="51"/>
-      <c r="E294" s="51"/>
-      <c r="F294" s="51"/>
-      <c r="G294" s="51"/>
-      <c r="H294" s="51"/>
-      <c r="I294" s="51"/>
-      <c r="J294" s="51"/>
-      <c r="K294" s="51"/>
-      <c r="L294" s="52"/>
+      <c r="D294" s="49"/>
+      <c r="E294" s="49"/>
+      <c r="F294" s="49"/>
+      <c r="G294" s="49"/>
+      <c r="H294" s="49"/>
+      <c r="I294" s="49"/>
+      <c r="J294" s="49"/>
+      <c r="K294" s="49"/>
+      <c r="L294" s="50"/>
     </row>
     <row r="295" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B295" s="10" t="s">
@@ -9285,35 +9283,35 @@
       <c r="B299" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C299" s="53" t="s">
+      <c r="C299" s="51" t="s">
         <v>313</v>
       </c>
-      <c r="D299" s="53"/>
-      <c r="E299" s="53"/>
-      <c r="F299" s="53"/>
-      <c r="G299" s="53"/>
-      <c r="H299" s="53"/>
-      <c r="I299" s="53"/>
-      <c r="J299" s="53"/>
-      <c r="K299" s="53"/>
-      <c r="L299" s="54"/>
+      <c r="D299" s="51"/>
+      <c r="E299" s="51"/>
+      <c r="F299" s="51"/>
+      <c r="G299" s="51"/>
+      <c r="H299" s="51"/>
+      <c r="I299" s="51"/>
+      <c r="J299" s="51"/>
+      <c r="K299" s="51"/>
+      <c r="L299" s="52"/>
     </row>
     <row r="300" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B300" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C300" s="45" t="s">
+      <c r="C300" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="D300" s="45"/>
-      <c r="E300" s="45"/>
-      <c r="F300" s="45"/>
-      <c r="G300" s="45"/>
-      <c r="H300" s="45"/>
-      <c r="I300" s="45"/>
-      <c r="J300" s="45"/>
-      <c r="K300" s="45"/>
-      <c r="L300" s="46"/>
+      <c r="D300" s="53"/>
+      <c r="E300" s="53"/>
+      <c r="F300" s="53"/>
+      <c r="G300" s="53"/>
+      <c r="H300" s="53"/>
+      <c r="I300" s="53"/>
+      <c r="J300" s="53"/>
+      <c r="K300" s="53"/>
+      <c r="L300" s="54"/>
     </row>
     <row r="301" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B301" s="10" t="s">
@@ -9430,18 +9428,18 @@
       <c r="B306" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C306" s="50" t="s">
+      <c r="C306" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="D306" s="51"/>
-      <c r="E306" s="51"/>
-      <c r="F306" s="51"/>
-      <c r="G306" s="51"/>
-      <c r="H306" s="51"/>
-      <c r="I306" s="51"/>
-      <c r="J306" s="51"/>
-      <c r="K306" s="51"/>
-      <c r="L306" s="52"/>
+      <c r="D306" s="49"/>
+      <c r="E306" s="49"/>
+      <c r="F306" s="49"/>
+      <c r="G306" s="49"/>
+      <c r="H306" s="49"/>
+      <c r="I306" s="49"/>
+      <c r="J306" s="49"/>
+      <c r="K306" s="49"/>
+      <c r="L306" s="50"/>
     </row>
     <row r="307" spans="2:12" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B307" s="10" t="s">
@@ -9571,6 +9569,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="C23:L23"/>
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="C3:L3"/>
+    <mergeCell ref="C247:L247"/>
+    <mergeCell ref="C248:L248"/>
+    <mergeCell ref="C169:L169"/>
+    <mergeCell ref="C170:L170"/>
+    <mergeCell ref="C158:L158"/>
+    <mergeCell ref="C159:L159"/>
+    <mergeCell ref="C180:L180"/>
+    <mergeCell ref="C231:L231"/>
+    <mergeCell ref="C232:L232"/>
+    <mergeCell ref="C181:L181"/>
+    <mergeCell ref="C120:L120"/>
+    <mergeCell ref="C121:L121"/>
+    <mergeCell ref="C113:L113"/>
+    <mergeCell ref="C305:L305"/>
+    <mergeCell ref="C306:L306"/>
+    <mergeCell ref="C73:L73"/>
+    <mergeCell ref="C103:L103"/>
+    <mergeCell ref="C104:L104"/>
+    <mergeCell ref="C299:L299"/>
+    <mergeCell ref="C300:L300"/>
+    <mergeCell ref="C135:L135"/>
+    <mergeCell ref="C136:L136"/>
+    <mergeCell ref="C293:L293"/>
+    <mergeCell ref="C294:L294"/>
+    <mergeCell ref="C144:L144"/>
+    <mergeCell ref="C145:L145"/>
+    <mergeCell ref="C74:L74"/>
+    <mergeCell ref="C280:L280"/>
+    <mergeCell ref="C281:L281"/>
+    <mergeCell ref="C197:L197"/>
+    <mergeCell ref="C196:L196"/>
+    <mergeCell ref="C62:L62"/>
+    <mergeCell ref="C63:L63"/>
+    <mergeCell ref="C68:L68"/>
+    <mergeCell ref="C69:L69"/>
+    <mergeCell ref="C165:L165"/>
+    <mergeCell ref="C175:L175"/>
+    <mergeCell ref="C176:L176"/>
+    <mergeCell ref="C90:L90"/>
+    <mergeCell ref="C91:L91"/>
+    <mergeCell ref="C98:L98"/>
+    <mergeCell ref="C99:L99"/>
+    <mergeCell ref="C114:L114"/>
+    <mergeCell ref="C276:L276"/>
+    <mergeCell ref="C261:L261"/>
+    <mergeCell ref="C210:L210"/>
+    <mergeCell ref="C211:L211"/>
+    <mergeCell ref="C54:L54"/>
+    <mergeCell ref="C55:L55"/>
+    <mergeCell ref="C260:L260"/>
+    <mergeCell ref="C219:L219"/>
+    <mergeCell ref="C220:L220"/>
+    <mergeCell ref="C226:L226"/>
+    <mergeCell ref="C227:L227"/>
+    <mergeCell ref="C255:L255"/>
+    <mergeCell ref="C256:L256"/>
+    <mergeCell ref="C275:L275"/>
+    <mergeCell ref="C188:L188"/>
+    <mergeCell ref="C189:L189"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C12:L12"/>
     <mergeCell ref="C130:L130"/>
@@ -9587,68 +9647,6 @@
     <mergeCell ref="C50:L50"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="C22:L22"/>
-    <mergeCell ref="C276:L276"/>
-    <mergeCell ref="C261:L261"/>
-    <mergeCell ref="C210:L210"/>
-    <mergeCell ref="C211:L211"/>
-    <mergeCell ref="C54:L54"/>
-    <mergeCell ref="C55:L55"/>
-    <mergeCell ref="C260:L260"/>
-    <mergeCell ref="C219:L219"/>
-    <mergeCell ref="C220:L220"/>
-    <mergeCell ref="C226:L226"/>
-    <mergeCell ref="C227:L227"/>
-    <mergeCell ref="C255:L255"/>
-    <mergeCell ref="C256:L256"/>
-    <mergeCell ref="C275:L275"/>
-    <mergeCell ref="C188:L188"/>
-    <mergeCell ref="C189:L189"/>
-    <mergeCell ref="C197:L197"/>
-    <mergeCell ref="C196:L196"/>
-    <mergeCell ref="C62:L62"/>
-    <mergeCell ref="C63:L63"/>
-    <mergeCell ref="C68:L68"/>
-    <mergeCell ref="C69:L69"/>
-    <mergeCell ref="C165:L165"/>
-    <mergeCell ref="C175:L175"/>
-    <mergeCell ref="C176:L176"/>
-    <mergeCell ref="C90:L90"/>
-    <mergeCell ref="C91:L91"/>
-    <mergeCell ref="C98:L98"/>
-    <mergeCell ref="C99:L99"/>
-    <mergeCell ref="C114:L114"/>
-    <mergeCell ref="C305:L305"/>
-    <mergeCell ref="C306:L306"/>
-    <mergeCell ref="C73:L73"/>
-    <mergeCell ref="C103:L103"/>
-    <mergeCell ref="C104:L104"/>
-    <mergeCell ref="C299:L299"/>
-    <mergeCell ref="C300:L300"/>
-    <mergeCell ref="C135:L135"/>
-    <mergeCell ref="C136:L136"/>
-    <mergeCell ref="C293:L293"/>
-    <mergeCell ref="C294:L294"/>
-    <mergeCell ref="C144:L144"/>
-    <mergeCell ref="C145:L145"/>
-    <mergeCell ref="C74:L74"/>
-    <mergeCell ref="C280:L280"/>
-    <mergeCell ref="C281:L281"/>
-    <mergeCell ref="C23:L23"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="C3:L3"/>
-    <mergeCell ref="C247:L247"/>
-    <mergeCell ref="C248:L248"/>
-    <mergeCell ref="C169:L169"/>
-    <mergeCell ref="C170:L170"/>
-    <mergeCell ref="C158:L158"/>
-    <mergeCell ref="C159:L159"/>
-    <mergeCell ref="C180:L180"/>
-    <mergeCell ref="C231:L231"/>
-    <mergeCell ref="C232:L232"/>
-    <mergeCell ref="C181:L181"/>
-    <mergeCell ref="C120:L120"/>
-    <mergeCell ref="C121:L121"/>
-    <mergeCell ref="C113:L113"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
